--- a/artfynd/A 54750-2025 artfynd.xlsx
+++ b/artfynd/A 54750-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130853402</v>
+        <v>130861157</v>
       </c>
       <c r="B2" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Djupbäcken, Djupbäcken, Jmt</t>
+          <t>Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442718</v>
+        <v>442745</v>
       </c>
       <c r="R2" t="n">
-        <v>7039654</v>
+        <v>7039681</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +743,14 @@
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:05</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130861157</v>
+        <v>130853402</v>
       </c>
       <c r="B3" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +788,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djupbäcken, Jmt</t>
+          <t>Djupbäcken, Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442745</v>
+        <v>442718</v>
       </c>
       <c r="R3" t="n">
-        <v>7039681</v>
+        <v>7039654</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,14 +850,19 @@
           <t>2026-01-24</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130853761</v>
+        <v>130861152</v>
       </c>
       <c r="B4" t="n">
-        <v>79222</v>
+        <v>91772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>230405</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djupbäcken, Djupbäcken, Jmt</t>
+          <t>Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442771</v>
+        <v>442868</v>
       </c>
       <c r="R4" t="n">
-        <v>7039709</v>
+        <v>7039767</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,19 +957,14 @@
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:05</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I stående levande gran med full längd.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130861152</v>
+        <v>130853761</v>
       </c>
       <c r="B5" t="n">
-        <v>91772</v>
+        <v>79222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,37 +1002,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>230405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupbäcken, Jmt</t>
+          <t>Djupbäcken, Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442868</v>
+        <v>442771</v>
       </c>
       <c r="R5" t="n">
-        <v>7039767</v>
+        <v>7039709</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,14 +1059,19 @@
           <t>2026-01-24</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>I stående levande gran med full längd.</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,12 +1086,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1711,7 +1711,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130861151</v>
+        <v>130853040</v>
       </c>
       <c r="B12" t="n">
         <v>57864</v>
@@ -1740,27 +1740,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djupbäcken, Jmt</t>
+          <t>Djupbäcken, Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442749</v>
+        <v>442679</v>
       </c>
       <c r="R12" t="n">
-        <v>7039568</v>
+        <v>7039590</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1787,14 +1784,19 @@
           <t>2026-01-24</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, enstaka på en gran. Mycket högt livsmiljövärde för tretåig hackspett kring fyndplatsen.</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1805,48 +1807,23 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130853040</v>
+        <v>130861151</v>
       </c>
       <c r="B13" t="n">
         <v>57864</v>
@@ -1875,24 +1852,27 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Djupbäcken, Djupbäcken, Jmt</t>
+          <t>Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442679</v>
+        <v>442749</v>
       </c>
       <c r="R13" t="n">
-        <v>7039590</v>
+        <v>7039568</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1919,19 +1899,14 @@
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:51</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, enstaka på en gran. Mycket högt livsmiljövärde för tretåig hackspett kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,16 +1917,41 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2054,6 +2054,550 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130865695</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Djupbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>442717</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7039603</v>
+      </c>
+      <c r="S15" t="n">
+        <v>11</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130865696</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91772</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Djupbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>442703</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7039596</v>
+      </c>
+      <c r="S16" t="n">
+        <v>9</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130865697</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Djupbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>442681</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7039580</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130865694</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Djupbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>442727</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7039590</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130865692</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Djupbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>442805</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7039508</v>
+      </c>
+      <c r="S19" t="n">
+        <v>9</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54750-2025 artfynd.xlsx
+++ b/artfynd/A 54750-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130861152</v>
+        <v>130853761</v>
       </c>
       <c r="B4" t="n">
-        <v>91772</v>
+        <v>79222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>230405</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djupbäcken, Jmt</t>
+          <t>Djupbäcken, Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442868</v>
+        <v>442771</v>
       </c>
       <c r="R4" t="n">
-        <v>7039767</v>
+        <v>7039709</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,14 +957,19 @@
           <t>2026-01-24</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>I stående levande gran med full längd.</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130853761</v>
+        <v>130861152</v>
       </c>
       <c r="B5" t="n">
-        <v>79222</v>
+        <v>91772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,37 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>230405</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupbäcken, Djupbäcken, Jmt</t>
+          <t>Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442771</v>
+        <v>442868</v>
       </c>
       <c r="R5" t="n">
-        <v>7039709</v>
+        <v>7039767</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1059,19 +1064,14 @@
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:05</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I stående levande gran med full längd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,12 +1086,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 54750-2025 artfynd.xlsx
+++ b/artfynd/A 54750-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130861157</v>
+        <v>130853402</v>
       </c>
       <c r="B2" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Djupbäcken, Jmt</t>
+          <t>Djupbäcken, Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442745</v>
+        <v>442718</v>
       </c>
       <c r="R2" t="n">
-        <v>7039681</v>
+        <v>7039654</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,14 +748,19 @@
           <t>2026-01-24</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130853402</v>
+        <v>130861157</v>
       </c>
       <c r="B3" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,42 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djupbäcken, Djupbäcken, Jmt</t>
+          <t>Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442718</v>
+        <v>442745</v>
       </c>
       <c r="R3" t="n">
-        <v>7039654</v>
+        <v>7039681</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,19 +855,14 @@
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:05</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130853761</v>
+        <v>130861152</v>
       </c>
       <c r="B4" t="n">
-        <v>79222</v>
+        <v>91772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>230405</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djupbäcken, Djupbäcken, Jmt</t>
+          <t>Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442771</v>
+        <v>442868</v>
       </c>
       <c r="R4" t="n">
-        <v>7039709</v>
+        <v>7039767</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,19 +957,14 @@
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:05</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I stående levande gran med full längd.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130861152</v>
+        <v>130853761</v>
       </c>
       <c r="B5" t="n">
-        <v>91772</v>
+        <v>79222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,37 +1002,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>230405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupbäcken, Jmt</t>
+          <t>Djupbäcken, Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442868</v>
+        <v>442771</v>
       </c>
       <c r="R5" t="n">
-        <v>7039767</v>
+        <v>7039709</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,14 +1059,19 @@
           <t>2026-01-24</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>I stående levande gran med full längd.</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,12 +1086,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130861155</v>
+        <v>130853040</v>
       </c>
       <c r="B11" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1620,37 +1620,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupbäcken, Jmt</t>
+          <t>Djupbäcken, Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442870</v>
+        <v>442679</v>
       </c>
       <c r="R11" t="n">
-        <v>7039632</v>
+        <v>7039590</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1677,14 +1682,19 @@
           <t>2026-01-24</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På död undertryck gran.</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1699,19 +1709,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130853040</v>
+        <v>130861151</v>
       </c>
       <c r="B12" t="n">
         <v>57864</v>
@@ -1740,24 +1750,27 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djupbäcken, Djupbäcken, Jmt</t>
+          <t>Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442679</v>
+        <v>442749</v>
       </c>
       <c r="R12" t="n">
-        <v>7039590</v>
+        <v>7039568</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1784,19 +1797,14 @@
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:51</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, enstaka på en gran. Mycket högt livsmiljövärde för tretåig hackspett kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,26 +1815,51 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130861151</v>
+        <v>130861155</v>
       </c>
       <c r="B13" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1834,42 +1867,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442749</v>
+        <v>442870</v>
       </c>
       <c r="R13" t="n">
-        <v>7039568</v>
+        <v>7039632</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1906,7 +1931,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på en gran. Mycket högt livsmiljövärde för tretåig hackspett kring fyndplatsen.</t>
+          <t>På död undertryck gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1917,31 +1942,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2598,6 +2598,225 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130865947</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Djupbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>442756</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7039676</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130865952</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Djupbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>442899</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7039717</v>
+      </c>
+      <c r="S21" t="n">
+        <v>14</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På dött träd</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54750-2025 artfynd.xlsx
+++ b/artfynd/A 54750-2025 artfynd.xlsx
@@ -1497,10 +1497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130861155</v>
+        <v>130861151</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1508,34 +1508,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442870</v>
+        <v>442749</v>
       </c>
       <c r="R10" t="n">
-        <v>7039632</v>
+        <v>7039568</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,7 +1580,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På död undertryck gran.</t>
+          <t>Ringhack, äldre, enstaka på en gran. Mycket högt livsmiljövärde för tretåig hackspett kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,6 +1591,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1599,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130861151</v>
+        <v>130861155</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1610,42 +1643,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442749</v>
+        <v>442870</v>
       </c>
       <c r="R11" t="n">
-        <v>7039568</v>
+        <v>7039632</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,7 +1707,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på en gran. Mycket högt livsmiljövärde för tretåig hackspett kring fyndplatsen.</t>
+          <t>På död undertryck gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,31 +1718,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">

--- a/artfynd/A 54750-2025 artfynd.xlsx
+++ b/artfynd/A 54750-2025 artfynd.xlsx
@@ -2379,7 +2379,7 @@
         <v>130865947</v>
       </c>
       <c r="B18" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>130865952</v>
       </c>
       <c r="B19" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 54750-2025 artfynd.xlsx
+++ b/artfynd/A 54750-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130861157</v>
+        <v>130861152</v>
       </c>
       <c r="B2" t="n">
-        <v>79244</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442745</v>
+        <v>442868</v>
       </c>
       <c r="R2" t="n">
-        <v>7039681</v>
+        <v>7039767</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>I stående levande gran med full längd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130861152</v>
+        <v>130861153</v>
       </c>
       <c r="B3" t="n">
-        <v>91805</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442868</v>
+        <v>442858</v>
       </c>
       <c r="R3" t="n">
-        <v>7039767</v>
+        <v>7039730</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I stående levande gran med full längd.</t>
+          <t>I 4-5 m granhögstubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130853761</v>
+        <v>130865696</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,37 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>230405</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djupbäcken, Djupbäcken, Jmt</t>
+          <t>Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442771</v>
+        <v>442703</v>
       </c>
       <c r="R4" t="n">
-        <v>7039709</v>
+        <v>7039596</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,14 +986,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130861156</v>
+        <v>130861155</v>
       </c>
       <c r="B5" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442897</v>
+        <v>442870</v>
       </c>
       <c r="R5" t="n">
-        <v>7039676</v>
+        <v>7039632</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På död stående gran med full längd.</t>
+          <t>På död undertryck gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,14 +1088,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130861158</v>
+        <v>130861156</v>
       </c>
       <c r="B6" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442743</v>
+        <v>442897</v>
       </c>
       <c r="R6" t="n">
-        <v>7039650</v>
+        <v>7039676</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På död stående gran med full längd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,32 +1190,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130861153</v>
+        <v>130861157</v>
       </c>
       <c r="B7" t="n">
-        <v>91805</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442858</v>
+        <v>442745</v>
       </c>
       <c r="R7" t="n">
-        <v>7039730</v>
+        <v>7039681</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>I 4-5 m granhögstubbe.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,47 +1292,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130853919</v>
+        <v>130861158</v>
       </c>
       <c r="B8" t="n">
-        <v>91933</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Högen, Högen, Jmt</t>
+          <t>Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442891</v>
+        <v>442743</v>
       </c>
       <c r="R8" t="n">
-        <v>7039668</v>
+        <v>7039650</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,19 +1360,14 @@
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:05</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1380,19 +1376,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1402,11 +1397,11 @@
         <v>130861159</v>
       </c>
       <c r="B9" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1501,56 +1496,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130861151</v>
+        <v>130865692</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442749</v>
+        <v>442805</v>
       </c>
       <c r="R10" t="n">
-        <v>7039568</v>
+        <v>7039508</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1577,14 +1564,19 @@
           <t>2026-01-24</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, enstaka på en gran. Mycket högt livsmiljövärde för tretåig hackspett kring fyndplatsen.</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1595,55 +1587,30 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130861155</v>
+        <v>130865694</v>
       </c>
       <c r="B11" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1671,13 +1638,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442870</v>
+        <v>442727</v>
       </c>
       <c r="R11" t="n">
-        <v>7039632</v>
+        <v>7039590</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1704,14 +1671,19 @@
           <t>2026-01-24</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På död undertryck gran.</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1726,42 +1698,46 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130861154</v>
+        <v>130865695</v>
       </c>
       <c r="B12" t="n">
-        <v>91829</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1769,13 +1745,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442747</v>
+        <v>442717</v>
       </c>
       <c r="R12" t="n">
-        <v>7039682</v>
+        <v>7039603</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1802,14 +1778,19 @@
           <t>2026-01-24</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>I granstubbe.</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1824,26 +1805,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130865695</v>
+        <v>130865947</v>
       </c>
       <c r="B13" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1871,13 +1852,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442717</v>
+        <v>442756</v>
       </c>
       <c r="R13" t="n">
-        <v>7039603</v>
+        <v>7039676</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1906,7 +1887,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1916,7 +1897,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1931,44 +1912,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130865696</v>
+        <v>130865952</v>
       </c>
       <c r="B14" t="n">
-        <v>91805</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1978,13 +1959,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442703</v>
+        <v>442899</v>
       </c>
       <c r="R14" t="n">
-        <v>7039596</v>
+        <v>7039717</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2013,7 +1994,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2023,7 +2004,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På dött träd</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2038,22 +2024,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130865697</v>
+        <v>130853040</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,21 +2067,25 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Djupbäcken, Jmt</t>
+          <t>Djupbäcken, Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442681</v>
+        <v>442679</v>
       </c>
       <c r="R15" t="n">
-        <v>7039580</v>
+        <v>7039590</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2124,7 +2114,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2134,12 +2124,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2166,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130865694</v>
+        <v>130853402</v>
       </c>
       <c r="B16" t="n">
-        <v>79244</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2177,37 +2167,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupbäcken, Jmt</t>
+          <t>Djupbäcken, Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442727</v>
+        <v>442718</v>
       </c>
       <c r="R16" t="n">
-        <v>7039590</v>
+        <v>7039654</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2236,7 +2234,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2246,7 +2244,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,10 +2276,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130865692</v>
+        <v>130861151</v>
       </c>
       <c r="B17" t="n">
-        <v>79244</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2284,37 +2287,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442805</v>
+        <v>442749</v>
       </c>
       <c r="R17" t="n">
-        <v>7039508</v>
+        <v>7039568</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2341,19 +2352,14 @@
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:20</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, enstaka på en gran. Mycket högt livsmiljövärde för tretåig hackspett kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2364,26 +2370,51 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130865947</v>
+        <v>130865697</v>
       </c>
       <c r="B18" t="n">
-        <v>79245</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2391,34 +2422,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442756</v>
+        <v>442681</v>
       </c>
       <c r="R18" t="n">
-        <v>7039676</v>
+        <v>7039580</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2450,7 +2485,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2460,7 +2495,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2475,39 +2515,39 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130865952</v>
+        <v>130853761</v>
       </c>
       <c r="B19" t="n">
-        <v>79245</v>
+        <v>79328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2518,17 +2558,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Djupbäcken, Jmt</t>
+          <t>Djupbäcken, Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442899</v>
+        <v>442771</v>
       </c>
       <c r="R19" t="n">
-        <v>7039717</v>
+        <v>7039709</v>
       </c>
       <c r="S19" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2557,7 +2597,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2567,12 +2607,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På dött träd</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2587,68 +2622,55 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130853402</v>
+        <v>130865950</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>91993</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6332881</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Djupbäcken, Djupbäcken, Jmt</t>
+          <t>Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442718</v>
+        <v>442793</v>
       </c>
       <c r="R20" t="n">
-        <v>7039654</v>
+        <v>7039674</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2677,7 +2699,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2687,12 +2709,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2707,68 +2724,55 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130853040</v>
+        <v>130865951</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>91928</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6332881</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Djupbäcken, Djupbäcken, Jmt</t>
+          <t>Djupbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442679</v>
+        <v>442858</v>
       </c>
       <c r="R21" t="n">
-        <v>7039590</v>
+        <v>7039724</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2797,7 +2801,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2807,12 +2811,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2827,12 +2826,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 54750-2025 artfynd.xlsx
+++ b/artfynd/A 54750-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130853040</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130865697</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130861152</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130861153</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130865696</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1321,6 +1351,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130861155</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1423,6 +1458,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130861156</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1525,6 +1565,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130861157</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1627,6 +1672,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130861158</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1729,6 +1779,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130861159</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1836,6 +1891,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130865692</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1943,6 +2003,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130865694</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130865695</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2157,6 +2227,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130865947</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2269,6 +2344,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130865952</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2389,6 +2469,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130853402</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2524,6 +2609,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130861151</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2631,6 +2721,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130853761</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2733,6 +2828,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130865950</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2835,8 +2935,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130865951</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>